--- a/server/plantillas/PLANTILLA_LLAMADAS_UNICAS.xlsx
+++ b/server/plantillas/PLANTILLA_LLAMADAS_UNICAS.xlsx
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -461,66 +461,57 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cómo se sube</v>
+        <v>Archivos del módulo</v>
       </c>
       <c r="B4" t="str">
-        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+        <v>Este módulo lleva 2 archivos, cada uno en su propia carga del Centro de cargas: (1) "Únicas de ingreso" — contestadas: Wolkvox, CDR; no contestadas: Wolkvox, reporte por skill y servicio. (2) "De salida" — Wolkvox, CDR. Esta plantilla es la de "Únicas de ingreso".</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Cómo se sube</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>Importante</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B6" t="str">
         <v>No cambie los nombres de las columnas. Los ejemplos de abajo son inventados: no los copie a la hoja de datos.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Columna</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Obligatoria</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Qué va</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Ejemplo (inventado)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>También se acepta como</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGENT_NAME</v>
+        <v>Columna</v>
       </c>
       <c r="B8" t="str">
-        <v>Sí</v>
+        <v>Obligatoria</v>
       </c>
       <c r="C8" t="str">
-        <v>Asesor que atendió.</v>
+        <v>Qué va</v>
       </c>
       <c r="D8" t="str">
-        <v>Asesor Ejemplo Uno</v>
+        <v>Ejemplo (inventado)</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>También se acepta como</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DATE</v>
+        <v>AGENT_NAME</v>
       </c>
       <c r="B9" t="str">
         <v>Sí</v>
       </c>
       <c r="C9" t="str">
-        <v>Fecha de la llamada.</v>
+        <v>Asesor que atendió.</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-08-01</v>
+        <v>Asesor Ejemplo Uno</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -528,16 +519,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TELEPHONE</v>
+        <v>DATE</v>
       </c>
       <c r="B10" t="str">
         <v>Sí</v>
       </c>
       <c r="C10" t="str">
-        <v>Número que llamó. Solo se usa en el navegador para contar una vez por día; nunca se envía ni se guarda.</v>
+        <v>Fecha de la llamada.</v>
       </c>
       <c r="D10" t="str">
-        <v>3000000000</v>
+        <v>2026-08-01</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -545,24 +536,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SKILL_NAME</v>
+        <v>TELEPHONE</v>
       </c>
       <c r="B11" t="str">
         <v>Sí</v>
       </c>
       <c r="C11" t="str">
-        <v>Línea o skill.</v>
+        <v>Número que llamó. Solo se usa en el navegador para contar una vez por día; nunca se envía ni se guarda.</v>
       </c>
       <c r="D11" t="str">
-        <v>SKILL SAC</v>
+        <v>3000000000</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SKILL_NAME</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Línea o skill.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>SKILL SAC</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/plantillas/PLANTILLA_LLAMADAS_UNICAS.xlsx
+++ b/server/plantillas/PLANTILLA_LLAMADAS_UNICAS.xlsx
@@ -448,7 +448,7 @@
         <v>De dónde sale</v>
       </c>
       <c r="B2" t="str">
-        <v>Wolkvox: Reportes → CDR → "1. Detalle de las llamadas", solo las de ingreso (sin las de salida).</v>
+        <v>Wolkvox, dos reportes en una sola hoja: las CONTESTADAS del CDR → "1. Detalle de las llamadas" (solo las de ingreso, con asesor) y las ABANDONADAS de "Skill y servicios → 2. Detalle llamadas abandonadas" (skill, teléfono y día, con AGENT_NAME vacío).</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +508,7 @@
         <v>Sí</v>
       </c>
       <c r="C9" t="str">
-        <v>Asesor que atendió.</v>
+        <v>Asesor que atendió. Vacío en las abandonadas (el reporte de abandonadas no trae asesor): una fila sin asesor cuenta como abandonada.</v>
       </c>
       <c r="D9" t="str">
         <v>Asesor Ejemplo Uno</v>
